--- a/R_analysis/output/tables/Tabela2_Regiao_anual.xlsx
+++ b/R_analysis/output/tables/Tabela2_Regiao_anual.xlsx
@@ -382,12 +382,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D2">
@@ -400,12 +400,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D3">
@@ -418,12 +418,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D4">
@@ -436,12 +436,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D5">
@@ -454,12 +454,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D6">
@@ -472,12 +472,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D7">
@@ -490,12 +490,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D8">
@@ -508,12 +508,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D9">
@@ -526,12 +526,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D10">
@@ -544,12 +544,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D11">
@@ -562,12 +562,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D12">
@@ -580,12 +580,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D13">
@@ -598,12 +598,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D14">
@@ -616,12 +616,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D15">
@@ -634,12 +634,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D16">
@@ -652,12 +652,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D17">
@@ -670,12 +670,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D18">
@@ -688,16 +688,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D19">
-        <v>1850</v>
+        <v>726</v>
       </c>
     </row>
     <row r="20">
@@ -706,16 +706,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D20">
-        <v>1927</v>
+        <v>774</v>
       </c>
     </row>
     <row r="21">
@@ -724,16 +724,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D21">
-        <v>2085</v>
+        <v>681</v>
       </c>
     </row>
     <row r="22">
@@ -742,16 +742,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D22">
-        <v>2311</v>
+        <v>649</v>
       </c>
     </row>
     <row r="23">
@@ -760,16 +760,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D23">
-        <v>3278</v>
+        <v>816</v>
       </c>
     </row>
     <row r="24">
@@ -778,16 +778,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D24">
-        <v>3794</v>
+        <v>894</v>
       </c>
     </row>
     <row r="25">
@@ -796,16 +796,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D25">
-        <v>4519</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="26">
@@ -814,16 +814,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D26">
-        <v>5121</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="27">
@@ -832,16 +832,16 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D27">
-        <v>6085</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="28">
@@ -850,16 +850,16 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D28">
-        <v>5971</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="29">
@@ -868,16 +868,16 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D29">
-        <v>7070</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="30">
@@ -886,16 +886,16 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D30">
-        <v>7966</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="31">
@@ -904,16 +904,16 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D31">
-        <v>7115</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="32">
@@ -922,16 +922,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D32">
-        <v>6743</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="33">
@@ -940,16 +940,16 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D33">
-        <v>8044</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="34">
@@ -958,16 +958,16 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D34">
-        <v>7347</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="35">
@@ -976,16 +976,16 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D35">
-        <v>7006</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="36">
@@ -994,16 +994,16 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D36">
-        <v>726</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="37">
@@ -1012,16 +1012,16 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D37">
-        <v>774</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="38">
@@ -1030,16 +1030,16 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D38">
-        <v>681</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="39">
@@ -1048,16 +1048,16 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D39">
-        <v>649</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="40">
@@ -1066,16 +1066,16 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D40">
-        <v>816</v>
+        <v>3278</v>
       </c>
     </row>
     <row r="41">
@@ -1084,16 +1084,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D41">
-        <v>894</v>
+        <v>3794</v>
       </c>
     </row>
     <row r="42">
@@ -1102,16 +1102,16 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D42">
-        <v>1081</v>
+        <v>4519</v>
       </c>
     </row>
     <row r="43">
@@ -1120,16 +1120,16 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D43">
-        <v>1228</v>
+        <v>5121</v>
       </c>
     </row>
     <row r="44">
@@ -1138,16 +1138,16 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D44">
-        <v>1442</v>
+        <v>6085</v>
       </c>
     </row>
     <row r="45">
@@ -1156,16 +1156,16 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D45">
-        <v>1754</v>
+        <v>5971</v>
       </c>
     </row>
     <row r="46">
@@ -1174,16 +1174,16 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D46">
-        <v>2207</v>
+        <v>7070</v>
       </c>
     </row>
     <row r="47">
@@ -1192,16 +1192,16 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D47">
-        <v>2243</v>
+        <v>7966</v>
       </c>
     </row>
     <row r="48">
@@ -1210,16 +1210,16 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D48">
-        <v>2258</v>
+        <v>7115</v>
       </c>
     </row>
     <row r="49">
@@ -1228,16 +1228,16 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D49">
-        <v>1769</v>
+        <v>6743</v>
       </c>
     </row>
     <row r="50">
@@ -1246,16 +1246,16 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D50">
-        <v>2281</v>
+        <v>8044</v>
       </c>
     </row>
     <row r="51">
@@ -1264,16 +1264,16 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D51">
-        <v>2395</v>
+        <v>7347</v>
       </c>
     </row>
     <row r="52">
@@ -1282,16 +1282,16 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D52">
-        <v>2453</v>
+        <v>7006</v>
       </c>
     </row>
     <row r="53">
@@ -1300,16 +1300,16 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D53">
-        <v>2212</v>
+        <v>370</v>
       </c>
     </row>
     <row r="54">
@@ -1318,16 +1318,16 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D54">
-        <v>2375</v>
+        <v>365</v>
       </c>
     </row>
     <row r="55">
@@ -1336,16 +1336,16 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D55">
-        <v>2455</v>
+        <v>585</v>
       </c>
     </row>
     <row r="56">
@@ -1354,16 +1354,16 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D56">
-        <v>3022</v>
+        <v>670</v>
       </c>
     </row>
     <row r="57">
@@ -1372,16 +1372,16 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D57">
-        <v>4164</v>
+        <v>921</v>
       </c>
     </row>
     <row r="58">
@@ -1390,16 +1390,16 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D58">
-        <v>5166</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="59">
@@ -1408,16 +1408,16 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D59">
-        <v>6158</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="60">
@@ -1426,16 +1426,16 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D60">
-        <v>7204</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="61">
@@ -1444,16 +1444,16 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D61">
-        <v>8339</v>
+        <v>2794</v>
       </c>
     </row>
     <row r="62">
@@ -1462,16 +1462,16 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D62">
-        <v>9296</v>
+        <v>3153</v>
       </c>
     </row>
     <row r="63">
@@ -1480,16 +1480,16 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D63">
-        <v>11101</v>
+        <v>3574</v>
       </c>
     </row>
     <row r="64">
@@ -1498,16 +1498,16 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D64">
-        <v>11620</v>
+        <v>3558</v>
       </c>
     </row>
     <row r="65">
@@ -1516,16 +1516,16 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D65">
-        <v>11432</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="66">
@@ -1534,16 +1534,16 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D66">
-        <v>10367</v>
+        <v>2931</v>
       </c>
     </row>
     <row r="67">
@@ -1552,16 +1552,16 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D67">
-        <v>11971</v>
+        <v>3609</v>
       </c>
     </row>
     <row r="68">
@@ -1570,16 +1570,16 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D68">
-        <v>11588</v>
+        <v>3524</v>
       </c>
     </row>
     <row r="69">
@@ -1588,16 +1588,16 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D69">
-        <v>10730</v>
+        <v>3380</v>
       </c>
     </row>
     <row r="70">
@@ -1606,16 +1606,16 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D70">
-        <v>370</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="71">
@@ -1624,16 +1624,16 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D71">
-        <v>365</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="72">
@@ -1642,16 +1642,16 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D72">
-        <v>585</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="73">
@@ -1660,16 +1660,16 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D73">
-        <v>670</v>
+        <v>3022</v>
       </c>
     </row>
     <row r="74">
@@ -1678,16 +1678,16 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D74">
-        <v>921</v>
+        <v>4164</v>
       </c>
     </row>
     <row r="75">
@@ -1696,16 +1696,16 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D75">
-        <v>1149</v>
+        <v>5166</v>
       </c>
     </row>
     <row r="76">
@@ -1714,16 +1714,16 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D76">
-        <v>1590</v>
+        <v>6158</v>
       </c>
     </row>
     <row r="77">
@@ -1732,16 +1732,16 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D77">
-        <v>1913</v>
+        <v>7204</v>
       </c>
     </row>
     <row r="78">
@@ -1750,16 +1750,16 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D78">
-        <v>2794</v>
+        <v>8339</v>
       </c>
     </row>
     <row r="79">
@@ -1768,16 +1768,16 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D79">
-        <v>3153</v>
+        <v>9296</v>
       </c>
     </row>
     <row r="80">
@@ -1786,16 +1786,16 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D80">
-        <v>3574</v>
+        <v>11101</v>
       </c>
     </row>
     <row r="81">
@@ -1804,16 +1804,16 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D81">
-        <v>3558</v>
+        <v>11620</v>
       </c>
     </row>
     <row r="82">
@@ -1822,16 +1822,16 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D82">
-        <v>3335</v>
+        <v>11432</v>
       </c>
     </row>
     <row r="83">
@@ -1840,16 +1840,16 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D83">
-        <v>2931</v>
+        <v>10367</v>
       </c>
     </row>
     <row r="84">
@@ -1858,16 +1858,16 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D84">
-        <v>3609</v>
+        <v>11971</v>
       </c>
     </row>
     <row r="85">
@@ -1876,16 +1876,16 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D85">
-        <v>3524</v>
+        <v>11588</v>
       </c>
     </row>
     <row r="86">
@@ -1894,16 +1894,16 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="D86">
-        <v>3380</v>
+        <v>10730</v>
       </c>
     </row>
     <row r="87">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D87">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D88">
@@ -1948,12 +1948,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D89">
@@ -1966,12 +1966,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D90">
@@ -1984,12 +1984,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D91">
@@ -2002,12 +2002,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D92">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D93">
@@ -2038,12 +2038,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D94">
@@ -2056,12 +2056,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D95">
@@ -2074,12 +2074,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D96">
@@ -2092,12 +2092,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D97">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D98">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D99">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D100">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D101">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D102">
@@ -2200,12 +2200,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
+          <t>Central-West</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D103">
@@ -2218,16 +2218,16 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D104">
-        <v>1716</v>
+        <v>994</v>
       </c>
     </row>
     <row r="105">
@@ -2236,16 +2236,16 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D105">
-        <v>1755</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="106">
@@ -2254,16 +2254,16 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D106">
-        <v>1986</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="107">
@@ -2272,16 +2272,16 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D107">
-        <v>2298</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="108">
@@ -2290,16 +2290,16 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D108">
-        <v>3146</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="109">
@@ -2308,16 +2308,16 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D109">
-        <v>3564</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="110">
@@ -2326,16 +2326,16 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D110">
-        <v>4152</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="111">
@@ -2344,16 +2344,16 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D111">
-        <v>5152</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="112">
@@ -2362,16 +2362,16 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D112">
-        <v>5949</v>
+        <v>3218</v>
       </c>
     </row>
     <row r="113">
@@ -2380,16 +2380,16 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D113">
-        <v>6540</v>
+        <v>3910</v>
       </c>
     </row>
     <row r="114">
@@ -2398,16 +2398,16 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D114">
-        <v>8891</v>
+        <v>4677</v>
       </c>
     </row>
     <row r="115">
@@ -2416,16 +2416,16 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D115">
-        <v>14722</v>
+        <v>5765</v>
       </c>
     </row>
     <row r="116">
@@ -2434,16 +2434,16 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D116">
-        <v>14563</v>
+        <v>6181</v>
       </c>
     </row>
     <row r="117">
@@ -2452,16 +2452,16 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D117">
-        <v>13976</v>
+        <v>6077</v>
       </c>
     </row>
     <row r="118">
@@ -2470,16 +2470,16 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D118">
-        <v>16848</v>
+        <v>8018</v>
       </c>
     </row>
     <row r="119">
@@ -2488,16 +2488,16 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D119">
-        <v>17304</v>
+        <v>8795</v>
       </c>
     </row>
     <row r="120">
@@ -2506,16 +2506,16 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D120">
-        <v>17458</v>
+        <v>8904</v>
       </c>
     </row>
     <row r="121">
@@ -2524,16 +2524,16 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D121">
-        <v>994</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="122">
@@ -2542,16 +2542,16 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D122">
-        <v>1167</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="123">
@@ -2560,16 +2560,16 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D123">
-        <v>1261</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="124">
@@ -2578,16 +2578,16 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D124">
-        <v>1273</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="125">
@@ -2596,16 +2596,16 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D125">
-        <v>1483</v>
+        <v>3146</v>
       </c>
     </row>
     <row r="126">
@@ -2614,16 +2614,16 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D126">
-        <v>1505</v>
+        <v>3564</v>
       </c>
     </row>
     <row r="127">
@@ -2632,16 +2632,16 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D127">
-        <v>1950</v>
+        <v>4152</v>
       </c>
     </row>
     <row r="128">
@@ -2650,16 +2650,16 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D128">
-        <v>2430</v>
+        <v>5152</v>
       </c>
     </row>
     <row r="129">
@@ -2668,16 +2668,16 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D129">
-        <v>3218</v>
+        <v>5949</v>
       </c>
     </row>
     <row r="130">
@@ -2686,16 +2686,16 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D130">
-        <v>3910</v>
+        <v>6540</v>
       </c>
     </row>
     <row r="131">
@@ -2704,16 +2704,16 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D131">
-        <v>4677</v>
+        <v>8891</v>
       </c>
     </row>
     <row r="132">
@@ -2722,16 +2722,16 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D132">
-        <v>5765</v>
+        <v>14722</v>
       </c>
     </row>
     <row r="133">
@@ -2740,16 +2740,16 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D133">
-        <v>6181</v>
+        <v>14563</v>
       </c>
     </row>
     <row r="134">
@@ -2758,16 +2758,16 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D134">
-        <v>6077</v>
+        <v>13976</v>
       </c>
     </row>
     <row r="135">
@@ -2776,16 +2776,16 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D135">
-        <v>8018</v>
+        <v>16848</v>
       </c>
     </row>
     <row r="136">
@@ -2794,16 +2794,16 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D136">
-        <v>8795</v>
+        <v>17304</v>
       </c>
     </row>
     <row r="137">
@@ -2812,16 +2812,16 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D137">
-        <v>8904</v>
+        <v>17458</v>
       </c>
     </row>
     <row r="138">
@@ -2830,16 +2830,16 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D138">
-        <v>1772</v>
+        <v>611</v>
       </c>
     </row>
     <row r="139">
@@ -2848,16 +2848,16 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D139">
-        <v>2581</v>
+        <v>687</v>
       </c>
     </row>
     <row r="140">
@@ -2866,16 +2866,16 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D140">
-        <v>2988</v>
+        <v>818</v>
       </c>
     </row>
     <row r="141">
@@ -2884,16 +2884,16 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D141">
-        <v>4037</v>
+        <v>971</v>
       </c>
     </row>
     <row r="142">
@@ -2902,16 +2902,16 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D142">
-        <v>6270</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="143">
@@ -2920,16 +2920,16 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D143">
-        <v>7812</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="144">
@@ -2938,16 +2938,16 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D144">
-        <v>9782</v>
+        <v>2679</v>
       </c>
     </row>
     <row r="145">
@@ -2956,16 +2956,16 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D145">
-        <v>12709</v>
+        <v>3733</v>
       </c>
     </row>
     <row r="146">
@@ -2974,16 +2974,16 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D146">
-        <v>14640</v>
+        <v>5844</v>
       </c>
     </row>
     <row r="147">
@@ -2992,16 +2992,16 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D147">
-        <v>17915</v>
+        <v>6763</v>
       </c>
     </row>
     <row r="148">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D148">
-        <v>23696</v>
+        <v>7879</v>
       </c>
     </row>
     <row r="149">
@@ -3028,16 +3028,16 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D149">
-        <v>28364</v>
+        <v>9342</v>
       </c>
     </row>
     <row r="150">
@@ -3046,16 +3046,16 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D150">
-        <v>29467</v>
+        <v>9659</v>
       </c>
     </row>
     <row r="151">
@@ -3064,16 +3064,16 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D151">
-        <v>30931</v>
+        <v>9184</v>
       </c>
     </row>
     <row r="152">
@@ -3082,16 +3082,16 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D152">
-        <v>33612</v>
+        <v>10814</v>
       </c>
     </row>
     <row r="153">
@@ -3100,16 +3100,16 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D153">
-        <v>38608</v>
+        <v>12223</v>
       </c>
     </row>
     <row r="154">
@@ -3118,16 +3118,16 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Sudeste</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D154">
-        <v>40420</v>
+        <v>12671</v>
       </c>
     </row>
     <row r="155">
@@ -3136,16 +3136,16 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D155">
-        <v>611</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="156">
@@ -3154,16 +3154,16 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D156">
-        <v>687</v>
+        <v>2581</v>
       </c>
     </row>
     <row r="157">
@@ -3172,16 +3172,16 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D157">
-        <v>818</v>
+        <v>2988</v>
       </c>
     </row>
     <row r="158">
@@ -3190,16 +3190,16 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D158">
-        <v>971</v>
+        <v>4037</v>
       </c>
     </row>
     <row r="159">
@@ -3208,16 +3208,16 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D159">
-        <v>1413</v>
+        <v>6270</v>
       </c>
     </row>
     <row r="160">
@@ -3226,16 +3226,16 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D160">
-        <v>1862</v>
+        <v>7812</v>
       </c>
     </row>
     <row r="161">
@@ -3244,16 +3244,16 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D161">
-        <v>2679</v>
+        <v>9782</v>
       </c>
     </row>
     <row r="162">
@@ -3262,16 +3262,16 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D162">
-        <v>3733</v>
+        <v>12709</v>
       </c>
     </row>
     <row r="163">
@@ -3280,16 +3280,16 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D163">
-        <v>5844</v>
+        <v>14640</v>
       </c>
     </row>
     <row r="164">
@@ -3298,16 +3298,16 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D164">
-        <v>6763</v>
+        <v>17915</v>
       </c>
     </row>
     <row r="165">
@@ -3316,16 +3316,16 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D165">
-        <v>7879</v>
+        <v>23696</v>
       </c>
     </row>
     <row r="166">
@@ -3334,16 +3334,16 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D166">
-        <v>9342</v>
+        <v>28364</v>
       </c>
     </row>
     <row r="167">
@@ -3352,16 +3352,16 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D167">
-        <v>9659</v>
+        <v>29467</v>
       </c>
     </row>
     <row r="168">
@@ -3370,16 +3370,16 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D168">
-        <v>9184</v>
+        <v>30931</v>
       </c>
     </row>
     <row r="169">
@@ -3388,16 +3388,16 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D169">
-        <v>10814</v>
+        <v>33612</v>
       </c>
     </row>
     <row r="170">
@@ -3406,16 +3406,16 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D170">
-        <v>12223</v>
+        <v>38608</v>
       </c>
     </row>
     <row r="171">
@@ -3424,16 +3424,16 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="D171">
-        <v>12671</v>
+        <v>40420</v>
       </c>
     </row>
   </sheetData>
